--- a/sampleprojects/SinusitisTherapy/excel/service2_creatinine.xlsx
+++ b/sampleprojects/SinusitisTherapy/excel/service2_creatinine.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>DT: Determine Creatinine Clearance</t>
   </si>
@@ -46,15 +46,18 @@
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
-    <t>Always compute CCr</t>
-  </si>
-  <si>
-    <t>true</t>
+    <t>Plasma creatinine was measured (0 is the unmeasured default)</t>
+  </si>
+  <si>
+    <t>patient.pcr &gt; 0</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -77,6 +80,12 @@
   </si>
   <si>
     <t>add "CCr estimated via Cockcroft-Gault from age, lean body weight, and plasma creatinine." to result.rationale</t>
+  </si>
+  <si>
+    <t>Rationale: no PCr, no CCr</t>
+  </si>
+  <si>
+    <t>add "CCr not computed: plasma creatinine was not supplied, so no renal dose adjustment was considered." to result.rationale</t>
   </si>
 </sst>
 </file>
@@ -661,55 +670,55 @@
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -765,58 +774,58 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -824,58 +833,117 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
